--- a/design/tables/TechnologyNode.xlsx
+++ b/design/tables/TechnologyNode.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TechnologyNode" sheetId="1" r:id="Rc9059d4c12e94f6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TechnologyNode" sheetId="1" r:id="Rf8ee1b633ec0459a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -309,6 +309,12 @@
       <x:c r="K1" s="3" t="str">
         <x:v>value</x:v>
       </x:c>
+      <x:c r="L1" s="3" t="str">
+        <x:v>iconKey</x:v>
+      </x:c>
+      <x:c r="M1" s="3" t="str">
+        <x:v>briefKey</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="3" t="str">
@@ -344,6 +350,12 @@
       <x:c r="K2" s="3" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="L2" s="3" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="M2" s="3" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="3" t="str">
@@ -379,6 +391,12 @@
       <x:c r="K3" s="3" t="str">
         <x:v>float</x:v>
       </x:c>
+      <x:c r="L3" s="3" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="M3" s="3" t="str">
+        <x:v>string</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="3" t="str">
@@ -414,6 +432,12 @@
       <x:c r="K4" s="3" t="str">
         <x:v>value</x:v>
       </x:c>
+      <x:c r="L4" s="3" t="str">
+        <x:v>iconKey</x:v>
+      </x:c>
+      <x:c r="M4" s="3" t="str">
+        <x:v>briefKey</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="3" t="str">
@@ -449,6 +473,12 @@
       <x:c r="K5" s="3" t="str">
         <x:v>value</x:v>
       </x:c>
+      <x:c r="L5" s="3" t="str">
+        <x:v>iconKey</x:v>
+      </x:c>
+      <x:c r="M5" s="3" t="str">
+        <x:v>briefKey</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="n">
@@ -465,7 +495,7 @@
       </x:c>
       <x:c r="E6" t="str"/>
       <x:c r="F6" t="n">
-        <x:v>180</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="G6" t="n">
         <x:v>0</x:v>
@@ -481,6 +511,12 @@
       </x:c>
       <x:c r="K6" t="n">
         <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L6" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M6" t="str">
+        <x:v>tech.node.sprout_1.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -500,7 +536,7 @@
         <x:v>sprout_1</x:v>
       </x:c>
       <x:c r="F7" t="n">
-        <x:v>600</x:v>
+        <x:v>2400</x:v>
       </x:c>
       <x:c r="G7" t="n">
         <x:v>2</x:v>
@@ -516,6 +552,12 @@
       </x:c>
       <x:c r="K7" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L7" t="str">
+        <x:v>ui:perk_S04</x:v>
+      </x:c>
+      <x:c r="M7" t="str">
+        <x:v>tech.node.sprout_2.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -535,7 +577,7 @@
         <x:v>sprout_2</x:v>
       </x:c>
       <x:c r="F8" t="n">
-        <x:v>1800</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G8" t="n">
         <x:v>5</x:v>
@@ -551,6 +593,12 @@
       </x:c>
       <x:c r="K8" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L8" t="str">
+        <x:v>ui:perk_G01</x:v>
+      </x:c>
+      <x:c r="M8" t="str">
+        <x:v>tech.node.sprout_3.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -570,7 +618,7 @@
         <x:v>sprout_3</x:v>
       </x:c>
       <x:c r="F9" t="n">
-        <x:v>5200</x:v>
+        <x:v>36000</x:v>
       </x:c>
       <x:c r="G9" t="n">
         <x:v>9</x:v>
@@ -586,6 +634,12 @@
       </x:c>
       <x:c r="K9" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L9" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M9" t="str">
+        <x:v>tech.node.sprout_4.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -605,7 +659,7 @@
         <x:v>sprout_4</x:v>
       </x:c>
       <x:c r="F10" t="n">
-        <x:v>14000</x:v>
+        <x:v>120000</x:v>
       </x:c>
       <x:c r="G10" t="n">
         <x:v>14</x:v>
@@ -621,6 +675,12 @@
       </x:c>
       <x:c r="K10" t="n">
         <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L10" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M10" t="str">
+        <x:v>tech.node.sprout_5.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -638,7 +698,7 @@
       </x:c>
       <x:c r="E11" t="str"/>
       <x:c r="F11" t="n">
-        <x:v>187</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="G11" t="n">
         <x:v>1</x:v>
@@ -654,6 +714,12 @@
       </x:c>
       <x:c r="K11" t="n">
         <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L11" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M11" t="str">
+        <x:v>tech.node.frost_1.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -673,7 +739,7 @@
         <x:v>frost_1</x:v>
       </x:c>
       <x:c r="F12" t="n">
-        <x:v>624</x:v>
+        <x:v>2496</x:v>
       </x:c>
       <x:c r="G12" t="n">
         <x:v>3</x:v>
@@ -689,6 +755,12 @@
       </x:c>
       <x:c r="K12" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L12" t="str">
+        <x:v>ui:perk_S04</x:v>
+      </x:c>
+      <x:c r="M12" t="str">
+        <x:v>tech.node.frost_2.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -708,7 +780,7 @@
         <x:v>frost_2</x:v>
       </x:c>
       <x:c r="F13" t="n">
-        <x:v>1872</x:v>
+        <x:v>10400</x:v>
       </x:c>
       <x:c r="G13" t="n">
         <x:v>6</x:v>
@@ -724,6 +796,12 @@
       </x:c>
       <x:c r="K13" t="n">
         <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="L13" t="str">
+        <x:v>ui:perk_S02</x:v>
+      </x:c>
+      <x:c r="M13" t="str">
+        <x:v>tech.node.frost_3.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -743,7 +821,7 @@
         <x:v>frost_3</x:v>
       </x:c>
       <x:c r="F14" t="n">
-        <x:v>5408</x:v>
+        <x:v>37440</x:v>
       </x:c>
       <x:c r="G14" t="n">
         <x:v>10</x:v>
@@ -759,6 +837,12 @@
       </x:c>
       <x:c r="K14" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L14" t="str">
+        <x:v>ui:perk_G01</x:v>
+      </x:c>
+      <x:c r="M14" t="str">
+        <x:v>tech.node.frost_4.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -778,7 +862,7 @@
         <x:v>frost_4</x:v>
       </x:c>
       <x:c r="F15" t="n">
-        <x:v>14560</x:v>
+        <x:v>124800</x:v>
       </x:c>
       <x:c r="G15" t="n">
         <x:v>15</x:v>
@@ -794,6 +878,12 @@
       </x:c>
       <x:c r="K15" t="n">
         <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L15" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M15" t="str">
+        <x:v>tech.node.frost_5.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -811,7 +901,7 @@
       </x:c>
       <x:c r="E16" t="str"/>
       <x:c r="F16" t="n">
-        <x:v>194</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="G16" t="n">
         <x:v>2</x:v>
@@ -827,6 +917,12 @@
       </x:c>
       <x:c r="K16" t="n">
         <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L16" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M16" t="str">
+        <x:v>tech.node.bloom_1.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -846,7 +942,7 @@
         <x:v>bloom_1</x:v>
       </x:c>
       <x:c r="F17" t="n">
-        <x:v>648</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="G17" t="n">
         <x:v>4</x:v>
@@ -862,6 +958,12 @@
       </x:c>
       <x:c r="K17" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L17" t="str">
+        <x:v>ui:perk_S04</x:v>
+      </x:c>
+      <x:c r="M17" t="str">
+        <x:v>tech.node.bloom_2.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -881,7 +983,7 @@
         <x:v>bloom_2</x:v>
       </x:c>
       <x:c r="F18" t="n">
-        <x:v>1944</x:v>
+        <x:v>10800</x:v>
       </x:c>
       <x:c r="G18" t="n">
         <x:v>7</x:v>
@@ -897,6 +999,12 @@
       </x:c>
       <x:c r="K18" t="n">
         <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="L18" t="str">
+        <x:v>ui:perk_S03</x:v>
+      </x:c>
+      <x:c r="M18" t="str">
+        <x:v>tech.node.bloom_3.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -916,7 +1024,7 @@
         <x:v>bloom_3</x:v>
       </x:c>
       <x:c r="F19" t="n">
-        <x:v>5616</x:v>
+        <x:v>38880</x:v>
       </x:c>
       <x:c r="G19" t="n">
         <x:v>11</x:v>
@@ -932,6 +1040,12 @@
       </x:c>
       <x:c r="K19" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L19" t="str">
+        <x:v>ui:perk_G01</x:v>
+      </x:c>
+      <x:c r="M19" t="str">
+        <x:v>tech.node.bloom_4.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -951,7 +1065,7 @@
         <x:v>bloom_4</x:v>
       </x:c>
       <x:c r="F20" t="n">
-        <x:v>15120</x:v>
+        <x:v>129600</x:v>
       </x:c>
       <x:c r="G20" t="n">
         <x:v>16</x:v>
@@ -967,6 +1081,12 @@
       </x:c>
       <x:c r="K20" t="n">
         <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L20" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M20" t="str">
+        <x:v>tech.node.bloom_5.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -984,7 +1104,7 @@
       </x:c>
       <x:c r="E21" t="str"/>
       <x:c r="F21" t="n">
-        <x:v>202</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="G21" t="n">
         <x:v>5</x:v>
@@ -1000,6 +1120,12 @@
       </x:c>
       <x:c r="K21" t="n">
         <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L21" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M21" t="str">
+        <x:v>tech.node.scope_1.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1019,7 +1145,7 @@
         <x:v>scope_1</x:v>
       </x:c>
       <x:c r="F22" t="n">
-        <x:v>672</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="G22" t="n">
         <x:v>7</x:v>
@@ -1035,6 +1161,12 @@
       </x:c>
       <x:c r="K22" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L22" t="str">
+        <x:v>ui:perk_S04</x:v>
+      </x:c>
+      <x:c r="M22" t="str">
+        <x:v>tech.node.scope_2.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1054,7 +1186,7 @@
         <x:v>scope_2</x:v>
       </x:c>
       <x:c r="F23" t="n">
-        <x:v>2016</x:v>
+        <x:v>11200</x:v>
       </x:c>
       <x:c r="G23" t="n">
         <x:v>10</x:v>
@@ -1070,6 +1202,12 @@
       </x:c>
       <x:c r="K23" t="n">
         <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="L23" t="str">
+        <x:v>ui:perk_S04</x:v>
+      </x:c>
+      <x:c r="M23" t="str">
+        <x:v>tech.node.scope_3.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1089,7 +1227,7 @@
         <x:v>scope_3</x:v>
       </x:c>
       <x:c r="F24" t="n">
-        <x:v>5824</x:v>
+        <x:v>40320</x:v>
       </x:c>
       <x:c r="G24" t="n">
         <x:v>14</x:v>
@@ -1105,6 +1243,12 @@
       </x:c>
       <x:c r="K24" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L24" t="str">
+        <x:v>ui:perk_G01</x:v>
+      </x:c>
+      <x:c r="M24" t="str">
+        <x:v>tech.node.scope_4.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1124,7 +1268,7 @@
         <x:v>scope_4</x:v>
       </x:c>
       <x:c r="F25" t="n">
-        <x:v>15680</x:v>
+        <x:v>134400</x:v>
       </x:c>
       <x:c r="G25" t="n">
         <x:v>19</x:v>
@@ -1140,6 +1284,12 @@
       </x:c>
       <x:c r="K25" t="n">
         <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L25" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M25" t="str">
+        <x:v>tech.node.scope_5.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1157,7 +1307,7 @@
       </x:c>
       <x:c r="E26" t="str"/>
       <x:c r="F26" t="n">
-        <x:v>209</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="G26" t="n">
         <x:v>7</x:v>
@@ -1173,6 +1323,12 @@
       </x:c>
       <x:c r="K26" t="n">
         <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L26" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M26" t="str">
+        <x:v>tech.node.spark_1.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1192,7 +1348,7 @@
         <x:v>spark_1</x:v>
       </x:c>
       <x:c r="F27" t="n">
-        <x:v>696</x:v>
+        <x:v>2784</x:v>
       </x:c>
       <x:c r="G27" t="n">
         <x:v>9</x:v>
@@ -1208,6 +1364,12 @@
       </x:c>
       <x:c r="K27" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L27" t="str">
+        <x:v>ui:perk_S04</x:v>
+      </x:c>
+      <x:c r="M27" t="str">
+        <x:v>tech.node.spark_2.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1227,7 +1389,7 @@
         <x:v>spark_2</x:v>
       </x:c>
       <x:c r="F28" t="n">
-        <x:v>2088</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="G28" t="n">
         <x:v>12</x:v>
@@ -1243,6 +1405,12 @@
       </x:c>
       <x:c r="K28" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L28" t="str">
+        <x:v>ui:perk_S05</x:v>
+      </x:c>
+      <x:c r="M28" t="str">
+        <x:v>tech.node.spark_3.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1262,7 +1430,7 @@
         <x:v>spark_3</x:v>
       </x:c>
       <x:c r="F29" t="n">
-        <x:v>6032</x:v>
+        <x:v>41760</x:v>
       </x:c>
       <x:c r="G29" t="n">
         <x:v>16</x:v>
@@ -1278,6 +1446,12 @@
       </x:c>
       <x:c r="K29" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L29" t="str">
+        <x:v>ui:perk_G01</x:v>
+      </x:c>
+      <x:c r="M29" t="str">
+        <x:v>tech.node.spark_4.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1297,7 +1471,7 @@
         <x:v>spark_4</x:v>
       </x:c>
       <x:c r="F30" t="n">
-        <x:v>16240</x:v>
+        <x:v>139200</x:v>
       </x:c>
       <x:c r="G30" t="n">
         <x:v>21</x:v>
@@ -1313,6 +1487,12 @@
       </x:c>
       <x:c r="K30" t="n">
         <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L30" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M30" t="str">
+        <x:v>tech.node.spark_5.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1330,7 +1510,7 @@
       </x:c>
       <x:c r="E31" t="str"/>
       <x:c r="F31" t="n">
-        <x:v>216</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="G31" t="n">
         <x:v>10</x:v>
@@ -1346,6 +1526,12 @@
       </x:c>
       <x:c r="K31" t="n">
         <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L31" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M31" t="str">
+        <x:v>tech.node.ember_1.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1365,7 +1551,7 @@
         <x:v>ember_1</x:v>
       </x:c>
       <x:c r="F32" t="n">
-        <x:v>720</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="G32" t="n">
         <x:v>12</x:v>
@@ -1381,6 +1567,12 @@
       </x:c>
       <x:c r="K32" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L32" t="str">
+        <x:v>ui:perk_S04</x:v>
+      </x:c>
+      <x:c r="M32" t="str">
+        <x:v>tech.node.ember_2.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1400,7 +1592,7 @@
         <x:v>ember_2</x:v>
       </x:c>
       <x:c r="F33" t="n">
-        <x:v>2160</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="G33" t="n">
         <x:v>15</x:v>
@@ -1416,6 +1608,12 @@
       </x:c>
       <x:c r="K33" t="n">
         <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="L33" t="str">
+        <x:v>ui:perk_S06</x:v>
+      </x:c>
+      <x:c r="M33" t="str">
+        <x:v>tech.node.ember_3.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -1435,7 +1633,7 @@
         <x:v>ember_3</x:v>
       </x:c>
       <x:c r="F34" t="n">
-        <x:v>6240</x:v>
+        <x:v>43200</x:v>
       </x:c>
       <x:c r="G34" t="n">
         <x:v>19</x:v>
@@ -1451,6 +1649,12 @@
       </x:c>
       <x:c r="K34" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L34" t="str">
+        <x:v>ui:perk_G01</x:v>
+      </x:c>
+      <x:c r="M34" t="str">
+        <x:v>tech.node.ember_4.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -1470,7 +1674,7 @@
         <x:v>ember_4</x:v>
       </x:c>
       <x:c r="F35" t="n">
-        <x:v>16800</x:v>
+        <x:v>144000</x:v>
       </x:c>
       <x:c r="G35" t="n">
         <x:v>24</x:v>
@@ -1486,6 +1690,12 @@
       </x:c>
       <x:c r="K35" t="n">
         <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L35" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M35" t="str">
+        <x:v>tech.node.ember_5.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1503,7 +1713,7 @@
       </x:c>
       <x:c r="E36" t="str"/>
       <x:c r="F36" t="n">
-        <x:v>223</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="G36" t="n">
         <x:v>12</x:v>
@@ -1519,6 +1729,12 @@
       </x:c>
       <x:c r="K36" t="n">
         <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L36" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M36" t="str">
+        <x:v>tech.node.mint_1.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -1538,7 +1754,7 @@
         <x:v>mint_1</x:v>
       </x:c>
       <x:c r="F37" t="n">
-        <x:v>744</x:v>
+        <x:v>2976</x:v>
       </x:c>
       <x:c r="G37" t="n">
         <x:v>14</x:v>
@@ -1554,6 +1770,12 @@
       </x:c>
       <x:c r="K37" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L37" t="str">
+        <x:v>ui:perk_S04</x:v>
+      </x:c>
+      <x:c r="M37" t="str">
+        <x:v>tech.node.mint_2.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -1573,7 +1795,7 @@
         <x:v>mint_2</x:v>
       </x:c>
       <x:c r="F38" t="n">
-        <x:v>2232</x:v>
+        <x:v>12400</x:v>
       </x:c>
       <x:c r="G38" t="n">
         <x:v>17</x:v>
@@ -1589,6 +1811,12 @@
       </x:c>
       <x:c r="K38" t="n">
         <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="L38" t="str">
+        <x:v>ui:perk_S07</x:v>
+      </x:c>
+      <x:c r="M38" t="str">
+        <x:v>tech.node.mint_3.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -1608,7 +1836,7 @@
         <x:v>mint_3</x:v>
       </x:c>
       <x:c r="F39" t="n">
-        <x:v>6448</x:v>
+        <x:v>44640</x:v>
       </x:c>
       <x:c r="G39" t="n">
         <x:v>21</x:v>
@@ -1624,6 +1852,12 @@
       </x:c>
       <x:c r="K39" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L39" t="str">
+        <x:v>ui:perk_G01</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>tech.node.mint_4.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -1643,7 +1877,7 @@
         <x:v>mint_4</x:v>
       </x:c>
       <x:c r="F40" t="n">
-        <x:v>17360</x:v>
+        <x:v>148800</x:v>
       </x:c>
       <x:c r="G40" t="n">
         <x:v>26</x:v>
@@ -1659,6 +1893,12 @@
       </x:c>
       <x:c r="K40" t="n">
         <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L40" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M40" t="str">
+        <x:v>tech.node.mint_5.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -1676,7 +1916,7 @@
       </x:c>
       <x:c r="E41" t="str"/>
       <x:c r="F41" t="n">
-        <x:v>230</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="G41" t="n">
         <x:v>15</x:v>
@@ -1692,6 +1932,12 @@
       </x:c>
       <x:c r="K41" t="n">
         <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L41" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M41" t="str">
+        <x:v>tech.node.fan_1.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -1711,7 +1957,7 @@
         <x:v>fan_1</x:v>
       </x:c>
       <x:c r="F42" t="n">
-        <x:v>768</x:v>
+        <x:v>3072</x:v>
       </x:c>
       <x:c r="G42" t="n">
         <x:v>17</x:v>
@@ -1727,6 +1973,12 @@
       </x:c>
       <x:c r="K42" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L42" t="str">
+        <x:v>ui:perk_S04</x:v>
+      </x:c>
+      <x:c r="M42" t="str">
+        <x:v>tech.node.fan_2.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -1746,7 +1998,7 @@
         <x:v>fan_2</x:v>
       </x:c>
       <x:c r="F43" t="n">
-        <x:v>2304</x:v>
+        <x:v>12800</x:v>
       </x:c>
       <x:c r="G43" t="n">
         <x:v>20</x:v>
@@ -1762,6 +2014,12 @@
       </x:c>
       <x:c r="K43" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L43" t="str">
+        <x:v>ui:perk_G01</x:v>
+      </x:c>
+      <x:c r="M43" t="str">
+        <x:v>tech.node.fan_3.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -1781,7 +2039,7 @@
         <x:v>fan_3</x:v>
       </x:c>
       <x:c r="F44" t="n">
-        <x:v>6656</x:v>
+        <x:v>46080</x:v>
       </x:c>
       <x:c r="G44" t="n">
         <x:v>24</x:v>
@@ -1797,6 +2055,12 @@
       </x:c>
       <x:c r="K44" t="n">
         <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="L44" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M44" t="str">
+        <x:v>tech.node.fan_4.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -1816,7 +2080,7 @@
         <x:v>fan_4</x:v>
       </x:c>
       <x:c r="F45" t="n">
-        <x:v>17920</x:v>
+        <x:v>153600</x:v>
       </x:c>
       <x:c r="G45" t="n">
         <x:v>29</x:v>
@@ -1832,6 +2096,12 @@
       </x:c>
       <x:c r="K45" t="n">
         <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L45" t="str">
+        <x:v>ui:perk_S01</x:v>
+      </x:c>
+      <x:c r="M45" t="str">
+        <x:v>tech.node.fan_5.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -1849,7 +2119,7 @@
       </x:c>
       <x:c r="E46" t="str"/>
       <x:c r="F46" t="n">
-        <x:v>238</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="G46" t="n">
         <x:v>0</x:v>
@@ -1865,6 +2135,12 @@
       </x:c>
       <x:c r="K46" t="n">
         <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="L46" t="str">
+        <x:v>ui:perk_E03</x:v>
+      </x:c>
+      <x:c r="M46" t="str">
+        <x:v>tech.node.logistics_1.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -1884,7 +2160,7 @@
         <x:v>logistics_1</x:v>
       </x:c>
       <x:c r="F47" t="n">
-        <x:v>792</x:v>
+        <x:v>3168</x:v>
       </x:c>
       <x:c r="G47" t="n">
         <x:v>2</x:v>
@@ -1900,6 +2176,12 @@
       </x:c>
       <x:c r="K47" t="n">
         <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L47" t="str">
+        <x:v>ui:perk_E04</x:v>
+      </x:c>
+      <x:c r="M47" t="str">
+        <x:v>tech.node.logistics_2.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -1919,7 +2201,7 @@
         <x:v>logistics_2</x:v>
       </x:c>
       <x:c r="F48" t="n">
-        <x:v>2376</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G48" t="n">
         <x:v>5</x:v>
@@ -1935,6 +2217,12 @@
       </x:c>
       <x:c r="K48" t="n">
         <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="L48" t="str">
+        <x:v>ui:perk_E03</x:v>
+      </x:c>
+      <x:c r="M48" t="str">
+        <x:v>tech.node.logistics_3.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -1954,7 +2242,7 @@
         <x:v>logistics_3</x:v>
       </x:c>
       <x:c r="F49" t="n">
-        <x:v>6864</x:v>
+        <x:v>47520</x:v>
       </x:c>
       <x:c r="G49" t="n">
         <x:v>9</x:v>
@@ -1970,6 +2258,12 @@
       </x:c>
       <x:c r="K49" t="n">
         <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L49" t="str">
+        <x:v>ui:perk_E04</x:v>
+      </x:c>
+      <x:c r="M49" t="str">
+        <x:v>tech.node.logistics_4.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -1989,7 +2283,7 @@
         <x:v>logistics_4</x:v>
       </x:c>
       <x:c r="F50" t="n">
-        <x:v>18480</x:v>
+        <x:v>158400</x:v>
       </x:c>
       <x:c r="G50" t="n">
         <x:v>14</x:v>
@@ -2005,6 +2299,12 @@
       </x:c>
       <x:c r="K50" t="n">
         <x:v>15</x:v>
+      </x:c>
+      <x:c r="L50" t="str">
+        <x:v>ui:perk_E01</x:v>
+      </x:c>
+      <x:c r="M50" t="str">
+        <x:v>tech.node.logistics_5.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -2022,7 +2322,7 @@
       </x:c>
       <x:c r="E51" t="str"/>
       <x:c r="F51" t="n">
-        <x:v>245</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="G51" t="n">
         <x:v>0</x:v>
@@ -2038,6 +2338,12 @@
       </x:c>
       <x:c r="K51" t="n">
         <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="L51" t="str">
+        <x:v>ui:perk_S02</x:v>
+      </x:c>
+      <x:c r="M51" t="str">
+        <x:v>tech.node.props_1.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -2057,7 +2363,7 @@
         <x:v>props_1</x:v>
       </x:c>
       <x:c r="F52" t="n">
-        <x:v>816</x:v>
+        <x:v>3264</x:v>
       </x:c>
       <x:c r="G52" t="n">
         <x:v>2</x:v>
@@ -2073,6 +2379,12 @@
       </x:c>
       <x:c r="K52" t="n">
         <x:v>8</x:v>
+      </x:c>
+      <x:c r="L52" t="str">
+        <x:v>ui:perk_E01</x:v>
+      </x:c>
+      <x:c r="M52" t="str">
+        <x:v>tech.node.props_2.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -2092,7 +2404,7 @@
         <x:v>props_2</x:v>
       </x:c>
       <x:c r="F53" t="n">
-        <x:v>2448</x:v>
+        <x:v>13600</x:v>
       </x:c>
       <x:c r="G53" t="n">
         <x:v>5</x:v>
@@ -2108,6 +2420,12 @@
       </x:c>
       <x:c r="K53" t="n">
         <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="L53" t="str">
+        <x:v>ui:perk_S02</x:v>
+      </x:c>
+      <x:c r="M53" t="str">
+        <x:v>tech.node.props_3.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -2127,7 +2445,7 @@
         <x:v>props_3</x:v>
       </x:c>
       <x:c r="F54" t="n">
-        <x:v>7072</x:v>
+        <x:v>48960</x:v>
       </x:c>
       <x:c r="G54" t="n">
         <x:v>9</x:v>
@@ -2143,6 +2461,12 @@
       </x:c>
       <x:c r="K54" t="n">
         <x:v>8</x:v>
+      </x:c>
+      <x:c r="L54" t="str">
+        <x:v>ui:perk_E01</x:v>
+      </x:c>
+      <x:c r="M54" t="str">
+        <x:v>tech.node.props_4.brief</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -2162,7 +2486,7 @@
         <x:v>props_4</x:v>
       </x:c>
       <x:c r="F55" t="n">
-        <x:v>19040</x:v>
+        <x:v>163200</x:v>
       </x:c>
       <x:c r="G55" t="n">
         <x:v>14</x:v>
@@ -2178,6 +2502,824 @@
       </x:c>
       <x:c r="K55" t="n">
         <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="L55" t="str">
+        <x:v>ui:perk_S02</x:v>
+      </x:c>
+      <x:c r="M55" t="str">
+        <x:v>tech.node.props_5.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>boss_1</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="D56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E56" t="str"/>
+      <x:c r="F56" t="n">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="G56" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H56" t="str">
+        <x:v>tech.node.boss_1.name</x:v>
+      </x:c>
+      <x:c r="I56" t="str">
+        <x:v>tech.node.boss_1.desc</x:v>
+      </x:c>
+      <x:c r="J56" t="str">
+        <x:v>bossDamage</x:v>
+      </x:c>
+      <x:c r="K56" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L56" t="str">
+        <x:v>ui:tech_boss</x:v>
+      </x:c>
+      <x:c r="M56" t="str">
+        <x:v>tech.node.boss_1.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>boss_2</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="D57" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E57" t="str">
+        <x:v>boss_1</x:v>
+      </x:c>
+      <x:c r="F57" t="n">
+        <x:v>3360</x:v>
+      </x:c>
+      <x:c r="G57" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H57" t="str">
+        <x:v>tech.node.boss_2.name</x:v>
+      </x:c>
+      <x:c r="I57" t="str">
+        <x:v>tech.node.boss_2.desc</x:v>
+      </x:c>
+      <x:c r="J57" t="str">
+        <x:v>bossDamage</x:v>
+      </x:c>
+      <x:c r="K57" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L57" t="str">
+        <x:v>ui:tech_boss</x:v>
+      </x:c>
+      <x:c r="M57" t="str">
+        <x:v>tech.node.boss_2.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B58" t="str">
+        <x:v>boss_3</x:v>
+      </x:c>
+      <x:c r="C58" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="D58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E58" t="str">
+        <x:v>boss_2</x:v>
+      </x:c>
+      <x:c r="F58" t="n">
+        <x:v>14000</x:v>
+      </x:c>
+      <x:c r="G58" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H58" t="str">
+        <x:v>tech.node.boss_3.name</x:v>
+      </x:c>
+      <x:c r="I58" t="str">
+        <x:v>tech.node.boss_3.desc</x:v>
+      </x:c>
+      <x:c r="J58" t="str">
+        <x:v>bossDamage</x:v>
+      </x:c>
+      <x:c r="K58" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L58" t="str">
+        <x:v>ui:tech_boss</x:v>
+      </x:c>
+      <x:c r="M58" t="str">
+        <x:v>tech.node.boss_3.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>boss_4</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="D59" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E59" t="str">
+        <x:v>boss_3</x:v>
+      </x:c>
+      <x:c r="F59" t="n">
+        <x:v>50400</x:v>
+      </x:c>
+      <x:c r="G59" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H59" t="str">
+        <x:v>tech.node.boss_4.name</x:v>
+      </x:c>
+      <x:c r="I59" t="str">
+        <x:v>tech.node.boss_4.desc</x:v>
+      </x:c>
+      <x:c r="J59" t="str">
+        <x:v>bossDamage</x:v>
+      </x:c>
+      <x:c r="K59" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L59" t="str">
+        <x:v>ui:tech_boss</x:v>
+      </x:c>
+      <x:c r="M59" t="str">
+        <x:v>tech.node.boss_4.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B60" t="str">
+        <x:v>boss_5</x:v>
+      </x:c>
+      <x:c r="C60" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="D60" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E60" t="str">
+        <x:v>boss_4</x:v>
+      </x:c>
+      <x:c r="F60" t="n">
+        <x:v>168000</x:v>
+      </x:c>
+      <x:c r="G60" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H60" t="str">
+        <x:v>tech.node.boss_5.name</x:v>
+      </x:c>
+      <x:c r="I60" t="str">
+        <x:v>tech.node.boss_5.desc</x:v>
+      </x:c>
+      <x:c r="J60" t="str">
+        <x:v>bossDamage</x:v>
+      </x:c>
+      <x:c r="K60" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="L60" t="str">
+        <x:v>ui:tech_boss</x:v>
+      </x:c>
+      <x:c r="M60" t="str">
+        <x:v>tech.node.boss_5.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B61" t="str">
+        <x:v>clearing_1</x:v>
+      </x:c>
+      <x:c r="C61" t="str">
+        <x:v>clearing</x:v>
+      </x:c>
+      <x:c r="D61" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E61" t="str"/>
+      <x:c r="F61" t="n">
+        <x:v>864</x:v>
+      </x:c>
+      <x:c r="G61" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H61" t="str">
+        <x:v>tech.node.clearing_1.name</x:v>
+      </x:c>
+      <x:c r="I61" t="str">
+        <x:v>tech.node.clearing_1.desc</x:v>
+      </x:c>
+      <x:c r="J61" t="str">
+        <x:v>obstacleDamage</x:v>
+      </x:c>
+      <x:c r="K61" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="L61" t="str">
+        <x:v>ui:tech_clear</x:v>
+      </x:c>
+      <x:c r="M61" t="str">
+        <x:v>tech.node.clearing_1.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B62" t="str">
+        <x:v>clearing_2</x:v>
+      </x:c>
+      <x:c r="C62" t="str">
+        <x:v>clearing</x:v>
+      </x:c>
+      <x:c r="D62" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E62" t="str">
+        <x:v>clearing_1</x:v>
+      </x:c>
+      <x:c r="F62" t="n">
+        <x:v>3456</x:v>
+      </x:c>
+      <x:c r="G62" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H62" t="str">
+        <x:v>tech.node.clearing_2.name</x:v>
+      </x:c>
+      <x:c r="I62" t="str">
+        <x:v>tech.node.clearing_2.desc</x:v>
+      </x:c>
+      <x:c r="J62" t="str">
+        <x:v>obstacleDamage</x:v>
+      </x:c>
+      <x:c r="K62" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="L62" t="str">
+        <x:v>ui:tech_clear</x:v>
+      </x:c>
+      <x:c r="M62" t="str">
+        <x:v>tech.node.clearing_2.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B63" t="str">
+        <x:v>clearing_3</x:v>
+      </x:c>
+      <x:c r="C63" t="str">
+        <x:v>clearing</x:v>
+      </x:c>
+      <x:c r="D63" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E63" t="str">
+        <x:v>clearing_2</x:v>
+      </x:c>
+      <x:c r="F63" t="n">
+        <x:v>14400</x:v>
+      </x:c>
+      <x:c r="G63" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H63" t="str">
+        <x:v>tech.node.clearing_3.name</x:v>
+      </x:c>
+      <x:c r="I63" t="str">
+        <x:v>tech.node.clearing_3.desc</x:v>
+      </x:c>
+      <x:c r="J63" t="str">
+        <x:v>obstacleDamage</x:v>
+      </x:c>
+      <x:c r="K63" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="L63" t="str">
+        <x:v>ui:tech_clear</x:v>
+      </x:c>
+      <x:c r="M63" t="str">
+        <x:v>tech.node.clearing_3.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B64" t="str">
+        <x:v>clearing_4</x:v>
+      </x:c>
+      <x:c r="C64" t="str">
+        <x:v>clearing</x:v>
+      </x:c>
+      <x:c r="D64" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E64" t="str">
+        <x:v>clearing_3</x:v>
+      </x:c>
+      <x:c r="F64" t="n">
+        <x:v>51840</x:v>
+      </x:c>
+      <x:c r="G64" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H64" t="str">
+        <x:v>tech.node.clearing_4.name</x:v>
+      </x:c>
+      <x:c r="I64" t="str">
+        <x:v>tech.node.clearing_4.desc</x:v>
+      </x:c>
+      <x:c r="J64" t="str">
+        <x:v>obstacleDamage</x:v>
+      </x:c>
+      <x:c r="K64" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L64" t="str">
+        <x:v>ui:tech_clear</x:v>
+      </x:c>
+      <x:c r="M64" t="str">
+        <x:v>tech.node.clearing_4.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B65" t="str">
+        <x:v>clearing_5</x:v>
+      </x:c>
+      <x:c r="C65" t="str">
+        <x:v>clearing</x:v>
+      </x:c>
+      <x:c r="D65" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E65" t="str">
+        <x:v>clearing_4</x:v>
+      </x:c>
+      <x:c r="F65" t="n">
+        <x:v>172800</x:v>
+      </x:c>
+      <x:c r="G65" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H65" t="str">
+        <x:v>tech.node.clearing_5.name</x:v>
+      </x:c>
+      <x:c r="I65" t="str">
+        <x:v>tech.node.clearing_5.desc</x:v>
+      </x:c>
+      <x:c r="J65" t="str">
+        <x:v>obstacleDamage</x:v>
+      </x:c>
+      <x:c r="K65" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L65" t="str">
+        <x:v>ui:tech_clear</x:v>
+      </x:c>
+      <x:c r="M65" t="str">
+        <x:v>tech.node.clearing_5.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>salvage_1</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>salvage</x:v>
+      </x:c>
+      <x:c r="D66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E66" t="str"/>
+      <x:c r="F66" t="n">
+        <x:v>888</x:v>
+      </x:c>
+      <x:c r="G66" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H66" t="str">
+        <x:v>tech.node.salvage_1.name</x:v>
+      </x:c>
+      <x:c r="I66" t="str">
+        <x:v>tech.node.salvage_1.desc</x:v>
+      </x:c>
+      <x:c r="J66" t="str">
+        <x:v>obstacleReward</x:v>
+      </x:c>
+      <x:c r="K66" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="L66" t="str">
+        <x:v>ui:tech_recycle</x:v>
+      </x:c>
+      <x:c r="M66" t="str">
+        <x:v>tech.node.salvage_1.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>salvage_2</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>salvage</x:v>
+      </x:c>
+      <x:c r="D67" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E67" t="str">
+        <x:v>salvage_1</x:v>
+      </x:c>
+      <x:c r="F67" t="n">
+        <x:v>3552</x:v>
+      </x:c>
+      <x:c r="G67" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H67" t="str">
+        <x:v>tech.node.salvage_2.name</x:v>
+      </x:c>
+      <x:c r="I67" t="str">
+        <x:v>tech.node.salvage_2.desc</x:v>
+      </x:c>
+      <x:c r="J67" t="str">
+        <x:v>obstacleReward</x:v>
+      </x:c>
+      <x:c r="K67" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="L67" t="str">
+        <x:v>ui:tech_recycle</x:v>
+      </x:c>
+      <x:c r="M67" t="str">
+        <x:v>tech.node.salvage_2.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>salvage_3</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>salvage</x:v>
+      </x:c>
+      <x:c r="D68" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E68" t="str">
+        <x:v>salvage_2</x:v>
+      </x:c>
+      <x:c r="F68" t="n">
+        <x:v>14800</x:v>
+      </x:c>
+      <x:c r="G68" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H68" t="str">
+        <x:v>tech.node.salvage_3.name</x:v>
+      </x:c>
+      <x:c r="I68" t="str">
+        <x:v>tech.node.salvage_3.desc</x:v>
+      </x:c>
+      <x:c r="J68" t="str">
+        <x:v>obstacleReward</x:v>
+      </x:c>
+      <x:c r="K68" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="L68" t="str">
+        <x:v>ui:tech_recycle</x:v>
+      </x:c>
+      <x:c r="M68" t="str">
+        <x:v>tech.node.salvage_3.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B69" t="str">
+        <x:v>salvage_4</x:v>
+      </x:c>
+      <x:c r="C69" t="str">
+        <x:v>salvage</x:v>
+      </x:c>
+      <x:c r="D69" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E69" t="str">
+        <x:v>salvage_3</x:v>
+      </x:c>
+      <x:c r="F69" t="n">
+        <x:v>53280</x:v>
+      </x:c>
+      <x:c r="G69" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H69" t="str">
+        <x:v>tech.node.salvage_4.name</x:v>
+      </x:c>
+      <x:c r="I69" t="str">
+        <x:v>tech.node.salvage_4.desc</x:v>
+      </x:c>
+      <x:c r="J69" t="str">
+        <x:v>obstacleReward</x:v>
+      </x:c>
+      <x:c r="K69" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="L69" t="str">
+        <x:v>ui:tech_recycle</x:v>
+      </x:c>
+      <x:c r="M69" t="str">
+        <x:v>tech.node.salvage_4.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>salvage_5</x:v>
+      </x:c>
+      <x:c r="C70" t="str">
+        <x:v>salvage</x:v>
+      </x:c>
+      <x:c r="D70" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E70" t="str">
+        <x:v>salvage_4</x:v>
+      </x:c>
+      <x:c r="F70" t="n">
+        <x:v>177600</x:v>
+      </x:c>
+      <x:c r="G70" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H70" t="str">
+        <x:v>tech.node.salvage_5.name</x:v>
+      </x:c>
+      <x:c r="I70" t="str">
+        <x:v>tech.node.salvage_5.desc</x:v>
+      </x:c>
+      <x:c r="J70" t="str">
+        <x:v>obstacleReward</x:v>
+      </x:c>
+      <x:c r="K70" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="L70" t="str">
+        <x:v>ui:tech_recycle</x:v>
+      </x:c>
+      <x:c r="M70" t="str">
+        <x:v>tech.node.salvage_5.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>supply_1</x:v>
+      </x:c>
+      <x:c r="C71" t="str">
+        <x:v>supply</x:v>
+      </x:c>
+      <x:c r="D71" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E71" t="str"/>
+      <x:c r="F71" t="n">
+        <x:v>912</x:v>
+      </x:c>
+      <x:c r="G71" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H71" t="str">
+        <x:v>tech.node.supply_1.name</x:v>
+      </x:c>
+      <x:c r="I71" t="str">
+        <x:v>tech.node.supply_1.desc</x:v>
+      </x:c>
+      <x:c r="J71" t="str">
+        <x:v>challengeXp</x:v>
+      </x:c>
+      <x:c r="K71" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L71" t="str">
+        <x:v>ui:tech_supply</x:v>
+      </x:c>
+      <x:c r="M71" t="str">
+        <x:v>tech.node.supply_1.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>supply_2</x:v>
+      </x:c>
+      <x:c r="C72" t="str">
+        <x:v>supply</x:v>
+      </x:c>
+      <x:c r="D72" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E72" t="str">
+        <x:v>supply_1</x:v>
+      </x:c>
+      <x:c r="F72" t="n">
+        <x:v>3648</x:v>
+      </x:c>
+      <x:c r="G72" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H72" t="str">
+        <x:v>tech.node.supply_2.name</x:v>
+      </x:c>
+      <x:c r="I72" t="str">
+        <x:v>tech.node.supply_2.desc</x:v>
+      </x:c>
+      <x:c r="J72" t="str">
+        <x:v>challengeXp</x:v>
+      </x:c>
+      <x:c r="K72" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L72" t="str">
+        <x:v>ui:tech_supply</x:v>
+      </x:c>
+      <x:c r="M72" t="str">
+        <x:v>tech.node.supply_2.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>supply_3</x:v>
+      </x:c>
+      <x:c r="C73" t="str">
+        <x:v>supply</x:v>
+      </x:c>
+      <x:c r="D73" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E73" t="str">
+        <x:v>supply_2</x:v>
+      </x:c>
+      <x:c r="F73" t="n">
+        <x:v>15200</x:v>
+      </x:c>
+      <x:c r="G73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H73" t="str">
+        <x:v>tech.node.supply_3.name</x:v>
+      </x:c>
+      <x:c r="I73" t="str">
+        <x:v>tech.node.supply_3.desc</x:v>
+      </x:c>
+      <x:c r="J73" t="str">
+        <x:v>challengeXp</x:v>
+      </x:c>
+      <x:c r="K73" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L73" t="str">
+        <x:v>ui:tech_supply</x:v>
+      </x:c>
+      <x:c r="M73" t="str">
+        <x:v>tech.node.supply_3.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B74" t="str">
+        <x:v>supply_4</x:v>
+      </x:c>
+      <x:c r="C74" t="str">
+        <x:v>supply</x:v>
+      </x:c>
+      <x:c r="D74" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E74" t="str">
+        <x:v>supply_3</x:v>
+      </x:c>
+      <x:c r="F74" t="n">
+        <x:v>54720</x:v>
+      </x:c>
+      <x:c r="G74" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H74" t="str">
+        <x:v>tech.node.supply_4.name</x:v>
+      </x:c>
+      <x:c r="I74" t="str">
+        <x:v>tech.node.supply_4.desc</x:v>
+      </x:c>
+      <x:c r="J74" t="str">
+        <x:v>challengeXp</x:v>
+      </x:c>
+      <x:c r="K74" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L74" t="str">
+        <x:v>ui:tech_supply</x:v>
+      </x:c>
+      <x:c r="M74" t="str">
+        <x:v>tech.node.supply_4.brief</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B75" t="str">
+        <x:v>supply_5</x:v>
+      </x:c>
+      <x:c r="C75" t="str">
+        <x:v>supply</x:v>
+      </x:c>
+      <x:c r="D75" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E75" t="str">
+        <x:v>supply_4</x:v>
+      </x:c>
+      <x:c r="F75" t="n">
+        <x:v>182400</x:v>
+      </x:c>
+      <x:c r="G75" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H75" t="str">
+        <x:v>tech.node.supply_5.name</x:v>
+      </x:c>
+      <x:c r="I75" t="str">
+        <x:v>tech.node.supply_5.desc</x:v>
+      </x:c>
+      <x:c r="J75" t="str">
+        <x:v>challengeXp</x:v>
+      </x:c>
+      <x:c r="K75" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L75" t="str">
+        <x:v>ui:tech_supply</x:v>
+      </x:c>
+      <x:c r="M75" t="str">
+        <x:v>tech.node.supply_5.brief</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
